--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N63_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N63_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.18642429374766</v>
+        <v>4.580293947733995</v>
       </c>
       <c r="D2" t="n">
-        <v>27.94373915193747</v>
+        <v>4.54085761218984</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
